--- a/templates/go-live-plan.xlsx
+++ b/templates/go-live-plan.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="1" r:id="R938d7691a72b49cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="明细表" sheetId="2" r:id="Rf3a8e02cbf944f95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="1" r:id="R753e67fc01324bda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="指挥链、回退与通知" sheetId="2" r:id="Rc9f796369f4a4a4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="上线执行" sheetId="3" r:id="Rfd74c523d9b24f66"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -37,7 +38,7 @@
     <x:font>
       <x:b/>
       <x:sz val="10"/>
-      <x:color rgb="FF1769E0"/>
+      <x:color rgb="FFB33A3A"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
     <x:font>
@@ -61,7 +62,7 @@
     <x:font>
       <x:b/>
       <x:sz val="9"/>
-      <x:color rgb="FF17365D"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
     <x:font>
@@ -71,14 +72,14 @@
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="13"/>
-      <x:color rgb="FF1769E0"/>
+      <x:sz val="9"/>
+      <x:color rgb="FF17365D"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
     <x:font>
       <x:b/>
-      <x:sz val="9"/>
-      <x:color rgb="FFFFFFFF"/>
+      <x:sz val="13"/>
+      <x:color rgb="FFB33A3A"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
     <x:font>
@@ -96,7 +97,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF17365D"/>
+        <x:fgColor rgb="FFB33A3A"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -106,22 +107,22 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCEEEE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF1769E0"/>
+        <x:fgColor rgb="FFF6F9FD"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF9E8"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFF6F9FD"/>
+        <x:fgColor rgb="FF17365D"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -175,7 +176,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="63">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -191,129 +192,166 @@
     <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
+    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="201" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
     </x:xf>
-    <x:xf numFmtId="201" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="200" fontId="8" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="6">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF257A50"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFE4F4EC"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FFA85B00"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFFF0D9"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
     <x:dxf>
       <x:font>
         <x:b/>
@@ -363,7 +401,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="go_live_plan_table" displayName="go_live_plan_table" ref="A8:I38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="go_live_plan_control" displayName="go_live_plan_control" ref="A4:G8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A4:G8"/>
+  <x:tableColumns count="7">
+    <x:tableColumn id="1" name="控制点"/>
+    <x:tableColumn id="2" name="触发条件/职责"/>
+    <x:tableColumn id="3" name="决策人"/>
+    <x:tableColumn id="4" name="执行人"/>
+    <x:tableColumn id="5" name="通知对象"/>
+    <x:tableColumn id="6" name="验证方式"/>
+    <x:tableColumn id="7" name="结果"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="go_live_plan_table" displayName="go_live_plan_table" ref="A8:I38" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A8:I38"/>
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="序号"/>
@@ -599,7 +653,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="8" t="str">
-        <x:v>SOP · 上线试运行  |  V2.0  |  蓝白医疗信息化模板</x:v>
+        <x:v>上线指挥 · 上线试运行  |  V2.1  |  差异化交付模板</x:v>
       </x:c>
       <x:c r="B2" s="8"/>
       <x:c r="C2" s="8"/>
@@ -620,88 +674,88 @@
       <x:c r="H3" s="1"/>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
-      <x:c r="A4" s="12" t="str">
+      <x:c r="A4" s="13" t="str">
         <x:v>模板用途</x:v>
       </x:c>
-      <x:c r="B4" s="16" t="str">
+      <x:c r="B4" s="17" t="str">
         <x:v>按时间顺序组织上线步骤、检查点、责任分工、完成标志和回退方案。</x:v>
       </x:c>
-      <x:c r="C4" s="16"/>
-      <x:c r="D4" s="16"/>
-      <x:c r="E4" s="16"/>
-      <x:c r="F4" s="16"/>
-      <x:c r="G4" s="16"/>
-      <x:c r="H4" s="16"/>
+      <x:c r="C4" s="17"/>
+      <x:c r="D4" s="17"/>
+      <x:c r="E4" s="17"/>
+      <x:c r="F4" s="17"/>
+      <x:c r="G4" s="17"/>
+      <x:c r="H4" s="17"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
-      <x:c r="A5" s="12" t="str">
+      <x:c r="A5" s="13" t="str">
         <x:v>推荐用法</x:v>
       </x:c>
-      <x:c r="B5" s="16" t="str">
-        <x:v>先在“明细表”填写项目基本信息，再逐行维护业务明细；交付前导出或打印后按项目要求签字归档。</x:v>
-      </x:c>
-      <x:c r="C5" s="16"/>
-      <x:c r="D5" s="16"/>
-      <x:c r="E5" s="16"/>
-      <x:c r="F5" s="16"/>
-      <x:c r="G5" s="16"/>
-      <x:c r="H5" s="16"/>
+      <x:c r="B5" s="17" t="str">
+        <x:v>先查看“指挥链、回退与通知”，再在“上线执行”逐行维护业务明细；交付前完成控制表中的确认项。</x:v>
+      </x:c>
+      <x:c r="C5" s="17"/>
+      <x:c r="D5" s="17"/>
+      <x:c r="E5" s="17"/>
+      <x:c r="F5" s="17"/>
+      <x:c r="G5" s="17"/>
+      <x:c r="H5" s="17"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="12" t="str">
+      <x:c r="A6" s="13" t="str">
         <x:v>输入区域</x:v>
       </x:c>
-      <x:c r="B6" s="16" t="str">
-        <x:v>浅黄色单元格为人工填写区；蓝色区域为标题或提示；绿色、橙色、红色用于状态提示。</x:v>
-      </x:c>
-      <x:c r="C6" s="16"/>
-      <x:c r="D6" s="16"/>
-      <x:c r="E6" s="16"/>
-      <x:c r="F6" s="16"/>
-      <x:c r="G6" s="16"/>
-      <x:c r="H6" s="16"/>
+      <x:c r="B6" s="17" t="str">
+        <x:v>浅色单元格为人工填写区；强调色区域为当前模板的控制点；绿色、橙色、红色用于状态提示。</x:v>
+      </x:c>
+      <x:c r="C6" s="17"/>
+      <x:c r="D6" s="17"/>
+      <x:c r="E6" s="17"/>
+      <x:c r="F6" s="17"/>
+      <x:c r="G6" s="17"/>
+      <x:c r="H6" s="17"/>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
-      <x:c r="A7" s="12" t="str">
+      <x:c r="A7" s="13" t="str">
         <x:v>日期格式</x:v>
       </x:c>
-      <x:c r="B7" s="16" t="str">
+      <x:c r="B7" s="17" t="str">
         <x:v>统一使用 YYYY-MM-DD；如需精确到时间，可使用 YYYY-MM-DD HH:MM。</x:v>
       </x:c>
-      <x:c r="C7" s="16"/>
-      <x:c r="D7" s="16"/>
-      <x:c r="E7" s="16"/>
-      <x:c r="F7" s="16"/>
-      <x:c r="G7" s="16"/>
-      <x:c r="H7" s="16"/>
+      <x:c r="C7" s="17"/>
+      <x:c r="D7" s="17"/>
+      <x:c r="E7" s="17"/>
+      <x:c r="F7" s="17"/>
+      <x:c r="G7" s="17"/>
+      <x:c r="H7" s="17"/>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
-      <x:c r="A8" s="12" t="str">
+      <x:c r="A8" s="13" t="str">
         <x:v>数据安全</x:v>
       </x:c>
-      <x:c r="B8" s="16" t="str">
+      <x:c r="B8" s="17" t="str">
         <x:v>不要填写明文口令、密钥或患者身份信息；敏感数据仅填写脱敏标识、引用编号或安全保管位置。</x:v>
       </x:c>
-      <x:c r="C8" s="16"/>
-      <x:c r="D8" s="16"/>
-      <x:c r="E8" s="16"/>
-      <x:c r="F8" s="16"/>
-      <x:c r="G8" s="16"/>
-      <x:c r="H8" s="16"/>
+      <x:c r="C8" s="17"/>
+      <x:c r="D8" s="17"/>
+      <x:c r="E8" s="17"/>
+      <x:c r="F8" s="17"/>
+      <x:c r="G8" s="17"/>
+      <x:c r="H8" s="17"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="12" t="str">
+      <x:c r="A9" s="13" t="str">
         <x:v>版本管理</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="str">
+      <x:c r="B9" s="17" t="str">
         <x:v>正式交付前填写版本号和确认日期；变更后另存新版本，不覆盖已签署的历史文件。</x:v>
       </x:c>
-      <x:c r="C9" s="16"/>
-      <x:c r="D9" s="16"/>
-      <x:c r="E9" s="16"/>
-      <x:c r="F9" s="16"/>
-      <x:c r="G9" s="16"/>
-      <x:c r="H9" s="16"/>
+      <x:c r="C9" s="17"/>
+      <x:c r="D9" s="17"/>
+      <x:c r="E9" s="17"/>
+      <x:c r="F9" s="17"/>
+      <x:c r="G9" s="17"/>
+      <x:c r="H9" s="17"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="1"/>
@@ -726,66 +780,66 @@
       <x:c r="H11" s="19"/>
     </x:row>
     <x:row r="12" ht="26" customHeight="1">
-      <x:c r="A12" s="23" t="str">
+      <x:c r="A12" s="22" t="str">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B12" s="22" t="str">
+      <x:c r="B12" s="21" t="str">
         <x:v>范围、版本和责任人已确认</x:v>
       </x:c>
-      <x:c r="C12" s="22" t="str"/>
-      <x:c r="D12" s="22" t="str"/>
-      <x:c r="E12" s="22" t="str"/>
-      <x:c r="F12" s="22" t="str"/>
-      <x:c r="G12" s="22" t="str"/>
-      <x:c r="H12" s="23" t="str">
+      <x:c r="C12" s="21" t="str"/>
+      <x:c r="D12" s="21" t="str"/>
+      <x:c r="E12" s="21" t="str"/>
+      <x:c r="F12" s="21" t="str"/>
+      <x:c r="G12" s="21" t="str"/>
+      <x:c r="H12" s="22" t="str">
         <x:v>☐</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26" customHeight="1">
-      <x:c r="A13" s="23" t="str">
+      <x:c r="A13" s="22" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="B13" s="22" t="str">
+      <x:c r="B13" s="21" t="str">
         <x:v>日期、状态和必填项已补齐</x:v>
       </x:c>
-      <x:c r="C13" s="22" t="str"/>
-      <x:c r="D13" s="22" t="str"/>
-      <x:c r="E13" s="22" t="str"/>
-      <x:c r="F13" s="22" t="str"/>
-      <x:c r="G13" s="22" t="str"/>
-      <x:c r="H13" s="23" t="str">
+      <x:c r="C13" s="21" t="str"/>
+      <x:c r="D13" s="21" t="str"/>
+      <x:c r="E13" s="21" t="str"/>
+      <x:c r="F13" s="21" t="str"/>
+      <x:c r="G13" s="21" t="str"/>
+      <x:c r="H13" s="22" t="str">
         <x:v>☐</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="26" customHeight="1">
-      <x:c r="A14" s="23" t="str">
+      <x:c r="A14" s="22" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B14" s="22" t="str">
+      <x:c r="B14" s="21" t="str">
         <x:v>敏感信息已脱敏或改用引用编号</x:v>
       </x:c>
-      <x:c r="C14" s="22" t="str"/>
-      <x:c r="D14" s="22" t="str"/>
-      <x:c r="E14" s="22" t="str"/>
-      <x:c r="F14" s="22" t="str"/>
-      <x:c r="G14" s="22" t="str"/>
-      <x:c r="H14" s="23" t="str">
+      <x:c r="C14" s="21" t="str"/>
+      <x:c r="D14" s="21" t="str"/>
+      <x:c r="E14" s="21" t="str"/>
+      <x:c r="F14" s="21" t="str"/>
+      <x:c r="G14" s="21" t="str"/>
+      <x:c r="H14" s="22" t="str">
         <x:v>☐</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="26" customHeight="1">
-      <x:c r="A15" s="23" t="str">
+      <x:c r="A15" s="22" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B15" s="22" t="str">
+      <x:c r="B15" s="21" t="str">
         <x:v>遗留问题已有责任人和计划日期</x:v>
       </x:c>
-      <x:c r="C15" s="22" t="str"/>
-      <x:c r="D15" s="22" t="str"/>
-      <x:c r="E15" s="22" t="str"/>
-      <x:c r="F15" s="22" t="str"/>
-      <x:c r="G15" s="22" t="str"/>
-      <x:c r="H15" s="23" t="str">
+      <x:c r="C15" s="21" t="str"/>
+      <x:c r="D15" s="21" t="str"/>
+      <x:c r="E15" s="21" t="str"/>
+      <x:c r="F15" s="21" t="str"/>
+      <x:c r="G15" s="21" t="str"/>
+      <x:c r="H15" s="22" t="str">
         <x:v>☐</x:v>
       </x:c>
     </x:row>
@@ -800,16 +854,16 @@
       <x:c r="H16" s="1"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="32" t="str">
-        <x:v>说明：本 Excel 版本适合批量维护明细；如需正式签字确认，可同时使用系统提供的同名 Word 版本。</x:v>
-      </x:c>
-      <x:c r="B17" s="33"/>
-      <x:c r="C17" s="33"/>
-      <x:c r="D17" s="33"/>
-      <x:c r="E17" s="33"/>
-      <x:c r="F17" s="33"/>
-      <x:c r="G17" s="33"/>
-      <x:c r="H17" s="34"/>
+      <x:c r="A17" s="31" t="str">
+        <x:v>说明：本模板采用“上线指挥”专用结构；完成业务明细后，请同步填写控制表并上传归档。</x:v>
+      </x:c>
+      <x:c r="B17" s="32"/>
+      <x:c r="C17" s="32"/>
+      <x:c r="D17" s="32"/>
+      <x:c r="E17" s="32"/>
+      <x:c r="F17" s="32"/>
+      <x:c r="G17" s="32"/>
+      <x:c r="H17" s="33"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -836,6 +890,200 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="26" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="42" customHeight="1">
+      <x:c r="A1" s="34" t="str">
+        <x:v>指挥链、回退与通知</x:v>
+      </x:c>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="34"/>
+      <x:c r="D1" s="34"/>
+      <x:c r="E1" s="34"/>
+      <x:c r="F1" s="34"/>
+      <x:c r="G1" s="34"/>
+    </x:row>
+    <x:row r="2" ht="25" customHeight="1">
+      <x:c r="A2" s="36" t="str">
+        <x:v>上线方案 · 上线指挥控制页  |  先确认本页，再完成业务明细</x:v>
+      </x:c>
+      <x:c r="B2" s="36"/>
+      <x:c r="C2" s="36"/>
+      <x:c r="D2" s="36"/>
+      <x:c r="E2" s="36"/>
+      <x:c r="F2" s="36"/>
+      <x:c r="G2" s="36"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="1"/>
+      <x:c r="D3" s="1"/>
+      <x:c r="E3" s="1"/>
+      <x:c r="F3" s="1"/>
+      <x:c r="G3" s="1"/>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="42" t="str">
+        <x:v>控制点</x:v>
+      </x:c>
+      <x:c r="B4" s="42" t="str">
+        <x:v>触发条件/职责</x:v>
+      </x:c>
+      <x:c r="C4" s="42" t="str">
+        <x:v>决策人</x:v>
+      </x:c>
+      <x:c r="D4" s="42" t="str">
+        <x:v>执行人</x:v>
+      </x:c>
+      <x:c r="E4" s="42" t="str">
+        <x:v>通知对象</x:v>
+      </x:c>
+      <x:c r="F4" s="42" t="str">
+        <x:v>验证方式</x:v>
+      </x:c>
+      <x:c r="G4" s="42" t="str">
+        <x:v>结果</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="34" customHeight="1">
+      <x:c r="A5" s="47" t="str">
+        <x:v>上线开始</x:v>
+      </x:c>
+      <x:c r="B5" s="47" t="str">
+        <x:v>范围、版本和窗口最终确认</x:v>
+      </x:c>
+      <x:c r="C5" s="46" t="str"/>
+      <x:c r="D5" s="46" t="str"/>
+      <x:c r="E5" s="46" t="str"/>
+      <x:c r="F5" s="46" t="str"/>
+      <x:c r="G5" s="46" t="str"/>
+    </x:row>
+    <x:row r="6" ht="34" customHeight="1">
+      <x:c r="A6" s="47" t="str">
+        <x:v>关键检查点</x:v>
+      </x:c>
+      <x:c r="B6" s="47" t="str">
+        <x:v>部署、迁移或业务验证完成</x:v>
+      </x:c>
+      <x:c r="C6" s="46" t="str"/>
+      <x:c r="D6" s="46" t="str"/>
+      <x:c r="E6" s="46" t="str"/>
+      <x:c r="F6" s="46" t="str"/>
+      <x:c r="G6" s="46" t="str"/>
+    </x:row>
+    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="A7" s="47" t="str">
+        <x:v>回退触发</x:v>
+      </x:c>
+      <x:c r="B7" s="47" t="str">
+        <x:v>达到已约定的失败或超时阈值</x:v>
+      </x:c>
+      <x:c r="C7" s="46" t="str"/>
+      <x:c r="D7" s="46" t="str"/>
+      <x:c r="E7" s="46" t="str"/>
+      <x:c r="F7" s="46" t="str"/>
+      <x:c r="G7" s="46" t="str"/>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
+      <x:c r="A8" s="47" t="str">
+        <x:v>上线完成</x:v>
+      </x:c>
+      <x:c r="B8" s="47" t="str">
+        <x:v>业务稳定、监控正常并完成通知</x:v>
+      </x:c>
+      <x:c r="C8" s="46" t="str"/>
+      <x:c r="D8" s="46" t="str"/>
+      <x:c r="E8" s="46" t="str"/>
+      <x:c r="F8" s="46" t="str"/>
+      <x:c r="G8" s="46" t="str"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="1"/>
+      <x:c r="B9" s="1"/>
+      <x:c r="C9" s="1"/>
+      <x:c r="D9" s="1"/>
+      <x:c r="E9" s="1"/>
+      <x:c r="F9" s="1"/>
+      <x:c r="G9" s="1"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="1"/>
+      <x:c r="B10" s="1"/>
+      <x:c r="C10" s="1"/>
+      <x:c r="D10" s="1"/>
+      <x:c r="E10" s="1"/>
+      <x:c r="F10" s="1"/>
+      <x:c r="G10" s="1"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="1"/>
+      <x:c r="B11" s="1"/>
+      <x:c r="C11" s="1"/>
+      <x:c r="D11" s="1"/>
+      <x:c r="E11" s="1"/>
+      <x:c r="F11" s="1"/>
+      <x:c r="G11" s="1"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="1"/>
+      <x:c r="B12" s="1"/>
+      <x:c r="C12" s="1"/>
+      <x:c r="D12" s="1"/>
+      <x:c r="E12" s="1"/>
+      <x:c r="F12" s="1"/>
+      <x:c r="G12" s="1"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="1"/>
+      <x:c r="B13" s="1"/>
+      <x:c r="C13" s="1"/>
+      <x:c r="D13" s="1"/>
+      <x:c r="E13" s="1"/>
+      <x:c r="F13" s="1"/>
+      <x:c r="G13" s="1"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="1"/>
+      <x:c r="B14" s="1"/>
+      <x:c r="C14" s="1"/>
+      <x:c r="D14" s="1"/>
+      <x:c r="E14" s="1"/>
+      <x:c r="F14" s="1"/>
+      <x:c r="G14" s="1"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="A2:G2"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="G5:G8">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="已"/>
+    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="待"/>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="G5:G8">
+      <x:formula1>"未确认,待处理,已确认,已完成,不适用"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8f7f7b630cf4bef"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="7" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
@@ -848,68 +1096,68 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
-      <x:c r="A1" s="35" t="str">
+      <x:c r="A1" s="34" t="str">
         <x:v>上线方案</x:v>
       </x:c>
-      <x:c r="B1" s="35"/>
-      <x:c r="C1" s="35"/>
-      <x:c r="D1" s="35"/>
-      <x:c r="E1" s="35"/>
-      <x:c r="F1" s="35"/>
-      <x:c r="G1" s="35"/>
-      <x:c r="H1" s="35"/>
-      <x:c r="I1" s="35"/>
+      <x:c r="B1" s="34"/>
+      <x:c r="C1" s="34"/>
+      <x:c r="D1" s="34"/>
+      <x:c r="E1" s="34"/>
+      <x:c r="F1" s="34"/>
+      <x:c r="G1" s="34"/>
+      <x:c r="H1" s="34"/>
+      <x:c r="I1" s="34"/>
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
-      <x:c r="A2" s="37" t="str">
-        <x:v>按时间顺序组织上线步骤、检查点、责任分工、完成标志和回退方案。  |  浅黄色为填写区</x:v>
-      </x:c>
-      <x:c r="B2" s="37"/>
-      <x:c r="C2" s="37"/>
-      <x:c r="D2" s="37"/>
-      <x:c r="E2" s="37"/>
-      <x:c r="F2" s="37"/>
-      <x:c r="G2" s="37"/>
-      <x:c r="H2" s="37"/>
-      <x:c r="I2" s="37"/>
+      <x:c r="A2" s="49" t="str">
+        <x:v>按时间顺序组织上线步骤、检查点、责任分工、完成标志和回退方案。  |  上线指挥专用明细</x:v>
+      </x:c>
+      <x:c r="B2" s="49"/>
+      <x:c r="C2" s="49"/>
+      <x:c r="D2" s="49"/>
+      <x:c r="E2" s="49"/>
+      <x:c r="F2" s="49"/>
+      <x:c r="G2" s="49"/>
+      <x:c r="H2" s="49"/>
+      <x:c r="I2" s="49"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="41" t="str">
+      <x:c r="A3" s="53" t="str">
         <x:v>项目名称</x:v>
       </x:c>
-      <x:c r="B3" s="44"/>
-      <x:c r="C3" s="44"/>
-      <x:c r="D3" s="41" t="str">
+      <x:c r="B3" s="54"/>
+      <x:c r="C3" s="54"/>
+      <x:c r="D3" s="53" t="str">
         <x:v>客户单位</x:v>
       </x:c>
-      <x:c r="E3" s="44"/>
-      <x:c r="F3" s="44"/>
-      <x:c r="G3" s="41" t="str">
+      <x:c r="E3" s="54"/>
+      <x:c r="F3" s="54"/>
+      <x:c r="G3" s="53" t="str">
         <x:v>项目经理</x:v>
       </x:c>
-      <x:c r="H3" s="44"/>
-      <x:c r="I3" s="44"/>
+      <x:c r="H3" s="54"/>
+      <x:c r="I3" s="54"/>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="41" t="str">
+      <x:c r="A4" s="53" t="str">
         <x:v>文档编号</x:v>
       </x:c>
-      <x:c r="B4" s="44"/>
-      <x:c r="C4" s="44"/>
-      <x:c r="D4" s="41" t="str">
+      <x:c r="B4" s="54"/>
+      <x:c r="C4" s="54"/>
+      <x:c r="D4" s="53" t="str">
         <x:v>版本</x:v>
       </x:c>
-      <x:c r="E4" s="44" t="str">
-        <x:v>V2.0</x:v>
-      </x:c>
-      <x:c r="F4" s="44" t="str">
-        <x:v>V2.0</x:v>
-      </x:c>
-      <x:c r="G4" s="41" t="str">
+      <x:c r="E4" s="54" t="str">
+        <x:v>V2.1</x:v>
+      </x:c>
+      <x:c r="F4" s="54" t="str">
+        <x:v>V2.1</x:v>
+      </x:c>
+      <x:c r="G4" s="53" t="str">
         <x:v>更新日期</x:v>
       </x:c>
-      <x:c r="H4" s="45"/>
-      <x:c r="I4" s="45"/>
+      <x:c r="H4" s="55"/>
+      <x:c r="I4" s="55"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="1"/>
@@ -923,31 +1171,31 @@
       <x:c r="I5" s="1"/>
     </x:row>
     <x:row r="6" ht="28" customHeight="1">
-      <x:c r="A6" s="41" t="str">
-        <x:v>记录数</x:v>
-      </x:c>
-      <x:c r="B6" s="50" t="n">
+      <x:c r="A6" s="53" t="str">
+        <x:v>事项数</x:v>
+      </x:c>
+      <x:c r="B6" s="60" t="n">
         <x:f>COUNTA(C9:C38)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C6" s="41" t="str">
-        <x:v>完成/通过</x:v>
-      </x:c>
-      <x:c r="D6" s="50" t="n">
+      <x:c r="C6" s="53" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="D6" s="60" t="n">
         <x:f>COUNTIF(I9:I38,"*已*")+COUNTIF(I9:I38,"通过")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E6" s="41" t="str">
-        <x:v>待处理</x:v>
-      </x:c>
-      <x:c r="F6" s="50" t="n">
+      <x:c r="E6" s="53" t="str">
+        <x:v>风险/待处理</x:v>
+      </x:c>
+      <x:c r="F6" s="60" t="n">
         <x:f>COUNTIF(I9:I38,"*待*")+COUNTIF(I9:I38,"不通过")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G6" s="41" t="str">
-        <x:v>状态待填</x:v>
-      </x:c>
-      <x:c r="H6" s="50" t="n">
+      <x:c r="G6" s="53" t="str">
+        <x:v>待开始</x:v>
+      </x:c>
+      <x:c r="H6" s="60" t="n">
         <x:f>COUNTBLANK(I9:I38)</x:f>
         <x:v>30</x:v>
       </x:c>
@@ -965,423 +1213,423 @@
       <x:c r="I7" s="1"/>
     </x:row>
     <x:row r="8" ht="32" customHeight="1">
-      <x:c r="A8" s="55" t="str">
+      <x:c r="A8" s="65" t="str">
         <x:v>序号</x:v>
       </x:c>
-      <x:c r="B8" s="55" t="str">
+      <x:c r="B8" s="65" t="str">
         <x:v>阶段</x:v>
       </x:c>
-      <x:c r="C8" s="55" t="str">
+      <x:c r="C8" s="65" t="str">
         <x:v>上线事项</x:v>
       </x:c>
-      <x:c r="D8" s="55" t="str">
+      <x:c r="D8" s="65" t="str">
         <x:v>执行步骤/检查点</x:v>
       </x:c>
-      <x:c r="E8" s="55" t="str">
+      <x:c r="E8" s="65" t="str">
         <x:v>负责人</x:v>
       </x:c>
-      <x:c r="F8" s="55" t="str">
+      <x:c r="F8" s="65" t="str">
         <x:v>计划时间</x:v>
       </x:c>
-      <x:c r="G8" s="55" t="str">
+      <x:c r="G8" s="65" t="str">
         <x:v>完成标志</x:v>
       </x:c>
-      <x:c r="H8" s="55" t="str">
+      <x:c r="H8" s="65" t="str">
         <x:v>回退方案</x:v>
       </x:c>
-      <x:c r="I8" s="55" t="str">
+      <x:c r="I8" s="65" t="str">
         <x:v>状态</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="60" t="str">
+      <x:c r="A9" s="67" t="str">
         <x:f>IF(C9="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B9" s="57"/>
-      <x:c r="C9" s="57"/>
-      <x:c r="D9" s="57"/>
-      <x:c r="E9" s="57"/>
-      <x:c r="F9" s="62"/>
-      <x:c r="G9" s="57"/>
-      <x:c r="H9" s="57"/>
-      <x:c r="I9" s="57"/>
+      <x:c r="B9" s="46"/>
+      <x:c r="C9" s="46"/>
+      <x:c r="D9" s="46"/>
+      <x:c r="E9" s="46"/>
+      <x:c r="F9" s="69"/>
+      <x:c r="G9" s="46"/>
+      <x:c r="H9" s="46"/>
+      <x:c r="I9" s="46"/>
     </x:row>
     <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="60" t="str">
+      <x:c r="A10" s="67" t="str">
         <x:f>IF(C10="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B10" s="57"/>
-      <x:c r="C10" s="57"/>
-      <x:c r="D10" s="57"/>
-      <x:c r="E10" s="57"/>
-      <x:c r="F10" s="62"/>
-      <x:c r="G10" s="57"/>
-      <x:c r="H10" s="57"/>
-      <x:c r="I10" s="57"/>
+      <x:c r="B10" s="46"/>
+      <x:c r="C10" s="46"/>
+      <x:c r="D10" s="46"/>
+      <x:c r="E10" s="46"/>
+      <x:c r="F10" s="69"/>
+      <x:c r="G10" s="46"/>
+      <x:c r="H10" s="46"/>
+      <x:c r="I10" s="46"/>
     </x:row>
     <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="60" t="str">
+      <x:c r="A11" s="67" t="str">
         <x:f>IF(C11="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B11" s="57"/>
-      <x:c r="C11" s="57"/>
-      <x:c r="D11" s="57"/>
-      <x:c r="E11" s="57"/>
-      <x:c r="F11" s="62"/>
-      <x:c r="G11" s="57"/>
-      <x:c r="H11" s="57"/>
-      <x:c r="I11" s="57"/>
+      <x:c r="B11" s="46"/>
+      <x:c r="C11" s="46"/>
+      <x:c r="D11" s="46"/>
+      <x:c r="E11" s="46"/>
+      <x:c r="F11" s="69"/>
+      <x:c r="G11" s="46"/>
+      <x:c r="H11" s="46"/>
+      <x:c r="I11" s="46"/>
     </x:row>
     <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="60" t="str">
+      <x:c r="A12" s="67" t="str">
         <x:f>IF(C12="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B12" s="57"/>
-      <x:c r="C12" s="57"/>
-      <x:c r="D12" s="57"/>
-      <x:c r="E12" s="57"/>
-      <x:c r="F12" s="62"/>
-      <x:c r="G12" s="57"/>
-      <x:c r="H12" s="57"/>
-      <x:c r="I12" s="57"/>
+      <x:c r="B12" s="46"/>
+      <x:c r="C12" s="46"/>
+      <x:c r="D12" s="46"/>
+      <x:c r="E12" s="46"/>
+      <x:c r="F12" s="69"/>
+      <x:c r="G12" s="46"/>
+      <x:c r="H12" s="46"/>
+      <x:c r="I12" s="46"/>
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="60" t="str">
+      <x:c r="A13" s="67" t="str">
         <x:f>IF(C13="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B13" s="57"/>
-      <x:c r="C13" s="57"/>
-      <x:c r="D13" s="57"/>
-      <x:c r="E13" s="57"/>
-      <x:c r="F13" s="62"/>
-      <x:c r="G13" s="57"/>
-      <x:c r="H13" s="57"/>
-      <x:c r="I13" s="57"/>
+      <x:c r="B13" s="46"/>
+      <x:c r="C13" s="46"/>
+      <x:c r="D13" s="46"/>
+      <x:c r="E13" s="46"/>
+      <x:c r="F13" s="69"/>
+      <x:c r="G13" s="46"/>
+      <x:c r="H13" s="46"/>
+      <x:c r="I13" s="46"/>
     </x:row>
     <x:row r="14" ht="30" customHeight="1">
-      <x:c r="A14" s="60" t="str">
+      <x:c r="A14" s="67" t="str">
         <x:f>IF(C14="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B14" s="57"/>
-      <x:c r="C14" s="57"/>
-      <x:c r="D14" s="57"/>
-      <x:c r="E14" s="57"/>
-      <x:c r="F14" s="62"/>
-      <x:c r="G14" s="57"/>
-      <x:c r="H14" s="57"/>
-      <x:c r="I14" s="57"/>
+      <x:c r="B14" s="46"/>
+      <x:c r="C14" s="46"/>
+      <x:c r="D14" s="46"/>
+      <x:c r="E14" s="46"/>
+      <x:c r="F14" s="69"/>
+      <x:c r="G14" s="46"/>
+      <x:c r="H14" s="46"/>
+      <x:c r="I14" s="46"/>
     </x:row>
     <x:row r="15" ht="30" customHeight="1">
-      <x:c r="A15" s="60" t="str">
+      <x:c r="A15" s="67" t="str">
         <x:f>IF(C15="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B15" s="57"/>
-      <x:c r="C15" s="57"/>
-      <x:c r="D15" s="57"/>
-      <x:c r="E15" s="57"/>
-      <x:c r="F15" s="62"/>
-      <x:c r="G15" s="57"/>
-      <x:c r="H15" s="57"/>
-      <x:c r="I15" s="57"/>
+      <x:c r="B15" s="46"/>
+      <x:c r="C15" s="46"/>
+      <x:c r="D15" s="46"/>
+      <x:c r="E15" s="46"/>
+      <x:c r="F15" s="69"/>
+      <x:c r="G15" s="46"/>
+      <x:c r="H15" s="46"/>
+      <x:c r="I15" s="46"/>
     </x:row>
     <x:row r="16" ht="30" customHeight="1">
-      <x:c r="A16" s="60" t="str">
+      <x:c r="A16" s="67" t="str">
         <x:f>IF(C16="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B16" s="57"/>
-      <x:c r="C16" s="57"/>
-      <x:c r="D16" s="57"/>
-      <x:c r="E16" s="57"/>
-      <x:c r="F16" s="62"/>
-      <x:c r="G16" s="57"/>
-      <x:c r="H16" s="57"/>
-      <x:c r="I16" s="57"/>
+      <x:c r="B16" s="46"/>
+      <x:c r="C16" s="46"/>
+      <x:c r="D16" s="46"/>
+      <x:c r="E16" s="46"/>
+      <x:c r="F16" s="69"/>
+      <x:c r="G16" s="46"/>
+      <x:c r="H16" s="46"/>
+      <x:c r="I16" s="46"/>
     </x:row>
     <x:row r="17" ht="30" customHeight="1">
-      <x:c r="A17" s="60" t="str">
+      <x:c r="A17" s="67" t="str">
         <x:f>IF(C17="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B17" s="57"/>
-      <x:c r="C17" s="57"/>
-      <x:c r="D17" s="57"/>
-      <x:c r="E17" s="57"/>
-      <x:c r="F17" s="62"/>
-      <x:c r="G17" s="57"/>
-      <x:c r="H17" s="57"/>
-      <x:c r="I17" s="57"/>
+      <x:c r="B17" s="46"/>
+      <x:c r="C17" s="46"/>
+      <x:c r="D17" s="46"/>
+      <x:c r="E17" s="46"/>
+      <x:c r="F17" s="69"/>
+      <x:c r="G17" s="46"/>
+      <x:c r="H17" s="46"/>
+      <x:c r="I17" s="46"/>
     </x:row>
     <x:row r="18" ht="30" customHeight="1">
-      <x:c r="A18" s="60" t="str">
+      <x:c r="A18" s="67" t="str">
         <x:f>IF(C18="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B18" s="57"/>
-      <x:c r="C18" s="57"/>
-      <x:c r="D18" s="57"/>
-      <x:c r="E18" s="57"/>
-      <x:c r="F18" s="62"/>
-      <x:c r="G18" s="57"/>
-      <x:c r="H18" s="57"/>
-      <x:c r="I18" s="57"/>
+      <x:c r="B18" s="46"/>
+      <x:c r="C18" s="46"/>
+      <x:c r="D18" s="46"/>
+      <x:c r="E18" s="46"/>
+      <x:c r="F18" s="69"/>
+      <x:c r="G18" s="46"/>
+      <x:c r="H18" s="46"/>
+      <x:c r="I18" s="46"/>
     </x:row>
     <x:row r="19" ht="30" customHeight="1">
-      <x:c r="A19" s="60" t="str">
+      <x:c r="A19" s="67" t="str">
         <x:f>IF(C19="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B19" s="57"/>
-      <x:c r="C19" s="57"/>
-      <x:c r="D19" s="57"/>
-      <x:c r="E19" s="57"/>
-      <x:c r="F19" s="62"/>
-      <x:c r="G19" s="57"/>
-      <x:c r="H19" s="57"/>
-      <x:c r="I19" s="57"/>
+      <x:c r="B19" s="46"/>
+      <x:c r="C19" s="46"/>
+      <x:c r="D19" s="46"/>
+      <x:c r="E19" s="46"/>
+      <x:c r="F19" s="69"/>
+      <x:c r="G19" s="46"/>
+      <x:c r="H19" s="46"/>
+      <x:c r="I19" s="46"/>
     </x:row>
     <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="60" t="str">
+      <x:c r="A20" s="67" t="str">
         <x:f>IF(C20="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B20" s="57"/>
-      <x:c r="C20" s="57"/>
-      <x:c r="D20" s="57"/>
-      <x:c r="E20" s="57"/>
-      <x:c r="F20" s="62"/>
-      <x:c r="G20" s="57"/>
-      <x:c r="H20" s="57"/>
-      <x:c r="I20" s="57"/>
+      <x:c r="B20" s="46"/>
+      <x:c r="C20" s="46"/>
+      <x:c r="D20" s="46"/>
+      <x:c r="E20" s="46"/>
+      <x:c r="F20" s="69"/>
+      <x:c r="G20" s="46"/>
+      <x:c r="H20" s="46"/>
+      <x:c r="I20" s="46"/>
     </x:row>
     <x:row r="21" ht="30" customHeight="1">
-      <x:c r="A21" s="60" t="str">
+      <x:c r="A21" s="67" t="str">
         <x:f>IF(C21="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B21" s="57"/>
-      <x:c r="C21" s="57"/>
-      <x:c r="D21" s="57"/>
-      <x:c r="E21" s="57"/>
-      <x:c r="F21" s="62"/>
-      <x:c r="G21" s="57"/>
-      <x:c r="H21" s="57"/>
-      <x:c r="I21" s="57"/>
+      <x:c r="B21" s="46"/>
+      <x:c r="C21" s="46"/>
+      <x:c r="D21" s="46"/>
+      <x:c r="E21" s="46"/>
+      <x:c r="F21" s="69"/>
+      <x:c r="G21" s="46"/>
+      <x:c r="H21" s="46"/>
+      <x:c r="I21" s="46"/>
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
-      <x:c r="A22" s="60" t="str">
+      <x:c r="A22" s="67" t="str">
         <x:f>IF(C22="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B22" s="57"/>
-      <x:c r="C22" s="57"/>
-      <x:c r="D22" s="57"/>
-      <x:c r="E22" s="57"/>
-      <x:c r="F22" s="62"/>
-      <x:c r="G22" s="57"/>
-      <x:c r="H22" s="57"/>
-      <x:c r="I22" s="57"/>
+      <x:c r="B22" s="46"/>
+      <x:c r="C22" s="46"/>
+      <x:c r="D22" s="46"/>
+      <x:c r="E22" s="46"/>
+      <x:c r="F22" s="69"/>
+      <x:c r="G22" s="46"/>
+      <x:c r="H22" s="46"/>
+      <x:c r="I22" s="46"/>
     </x:row>
     <x:row r="23" ht="30" customHeight="1">
-      <x:c r="A23" s="60" t="str">
+      <x:c r="A23" s="67" t="str">
         <x:f>IF(C23="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B23" s="57"/>
-      <x:c r="C23" s="57"/>
-      <x:c r="D23" s="57"/>
-      <x:c r="E23" s="57"/>
-      <x:c r="F23" s="62"/>
-      <x:c r="G23" s="57"/>
-      <x:c r="H23" s="57"/>
-      <x:c r="I23" s="57"/>
+      <x:c r="B23" s="46"/>
+      <x:c r="C23" s="46"/>
+      <x:c r="D23" s="46"/>
+      <x:c r="E23" s="46"/>
+      <x:c r="F23" s="69"/>
+      <x:c r="G23" s="46"/>
+      <x:c r="H23" s="46"/>
+      <x:c r="I23" s="46"/>
     </x:row>
     <x:row r="24" ht="30" customHeight="1">
-      <x:c r="A24" s="60" t="str">
+      <x:c r="A24" s="67" t="str">
         <x:f>IF(C24="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B24" s="57"/>
-      <x:c r="C24" s="57"/>
-      <x:c r="D24" s="57"/>
-      <x:c r="E24" s="57"/>
-      <x:c r="F24" s="62"/>
-      <x:c r="G24" s="57"/>
-      <x:c r="H24" s="57"/>
-      <x:c r="I24" s="57"/>
+      <x:c r="B24" s="46"/>
+      <x:c r="C24" s="46"/>
+      <x:c r="D24" s="46"/>
+      <x:c r="E24" s="46"/>
+      <x:c r="F24" s="69"/>
+      <x:c r="G24" s="46"/>
+      <x:c r="H24" s="46"/>
+      <x:c r="I24" s="46"/>
     </x:row>
     <x:row r="25" ht="30" customHeight="1">
-      <x:c r="A25" s="60" t="str">
+      <x:c r="A25" s="67" t="str">
         <x:f>IF(C25="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B25" s="57"/>
-      <x:c r="C25" s="57"/>
-      <x:c r="D25" s="57"/>
-      <x:c r="E25" s="57"/>
-      <x:c r="F25" s="62"/>
-      <x:c r="G25" s="57"/>
-      <x:c r="H25" s="57"/>
-      <x:c r="I25" s="57"/>
+      <x:c r="B25" s="46"/>
+      <x:c r="C25" s="46"/>
+      <x:c r="D25" s="46"/>
+      <x:c r="E25" s="46"/>
+      <x:c r="F25" s="69"/>
+      <x:c r="G25" s="46"/>
+      <x:c r="H25" s="46"/>
+      <x:c r="I25" s="46"/>
     </x:row>
     <x:row r="26" ht="30" customHeight="1">
-      <x:c r="A26" s="60" t="str">
+      <x:c r="A26" s="67" t="str">
         <x:f>IF(C26="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B26" s="57"/>
-      <x:c r="C26" s="57"/>
-      <x:c r="D26" s="57"/>
-      <x:c r="E26" s="57"/>
-      <x:c r="F26" s="62"/>
-      <x:c r="G26" s="57"/>
-      <x:c r="H26" s="57"/>
-      <x:c r="I26" s="57"/>
+      <x:c r="B26" s="46"/>
+      <x:c r="C26" s="46"/>
+      <x:c r="D26" s="46"/>
+      <x:c r="E26" s="46"/>
+      <x:c r="F26" s="69"/>
+      <x:c r="G26" s="46"/>
+      <x:c r="H26" s="46"/>
+      <x:c r="I26" s="46"/>
     </x:row>
     <x:row r="27" ht="30" customHeight="1">
-      <x:c r="A27" s="60" t="str">
+      <x:c r="A27" s="67" t="str">
         <x:f>IF(C27="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B27" s="57"/>
-      <x:c r="C27" s="57"/>
-      <x:c r="D27" s="57"/>
-      <x:c r="E27" s="57"/>
-      <x:c r="F27" s="62"/>
-      <x:c r="G27" s="57"/>
-      <x:c r="H27" s="57"/>
-      <x:c r="I27" s="57"/>
+      <x:c r="B27" s="46"/>
+      <x:c r="C27" s="46"/>
+      <x:c r="D27" s="46"/>
+      <x:c r="E27" s="46"/>
+      <x:c r="F27" s="69"/>
+      <x:c r="G27" s="46"/>
+      <x:c r="H27" s="46"/>
+      <x:c r="I27" s="46"/>
     </x:row>
     <x:row r="28" ht="30" customHeight="1">
-      <x:c r="A28" s="60" t="str">
+      <x:c r="A28" s="67" t="str">
         <x:f>IF(C28="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B28" s="57"/>
-      <x:c r="C28" s="57"/>
-      <x:c r="D28" s="57"/>
-      <x:c r="E28" s="57"/>
-      <x:c r="F28" s="62"/>
-      <x:c r="G28" s="57"/>
-      <x:c r="H28" s="57"/>
-      <x:c r="I28" s="57"/>
+      <x:c r="B28" s="46"/>
+      <x:c r="C28" s="46"/>
+      <x:c r="D28" s="46"/>
+      <x:c r="E28" s="46"/>
+      <x:c r="F28" s="69"/>
+      <x:c r="G28" s="46"/>
+      <x:c r="H28" s="46"/>
+      <x:c r="I28" s="46"/>
     </x:row>
     <x:row r="29" ht="30" customHeight="1">
-      <x:c r="A29" s="60" t="str">
+      <x:c r="A29" s="67" t="str">
         <x:f>IF(C29="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B29" s="57"/>
-      <x:c r="C29" s="57"/>
-      <x:c r="D29" s="57"/>
-      <x:c r="E29" s="57"/>
-      <x:c r="F29" s="62"/>
-      <x:c r="G29" s="57"/>
-      <x:c r="H29" s="57"/>
-      <x:c r="I29" s="57"/>
+      <x:c r="B29" s="46"/>
+      <x:c r="C29" s="46"/>
+      <x:c r="D29" s="46"/>
+      <x:c r="E29" s="46"/>
+      <x:c r="F29" s="69"/>
+      <x:c r="G29" s="46"/>
+      <x:c r="H29" s="46"/>
+      <x:c r="I29" s="46"/>
     </x:row>
     <x:row r="30" ht="30" customHeight="1">
-      <x:c r="A30" s="60" t="str">
+      <x:c r="A30" s="67" t="str">
         <x:f>IF(C30="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B30" s="57"/>
-      <x:c r="C30" s="57"/>
-      <x:c r="D30" s="57"/>
-      <x:c r="E30" s="57"/>
-      <x:c r="F30" s="62"/>
-      <x:c r="G30" s="57"/>
-      <x:c r="H30" s="57"/>
-      <x:c r="I30" s="57"/>
+      <x:c r="B30" s="46"/>
+      <x:c r="C30" s="46"/>
+      <x:c r="D30" s="46"/>
+      <x:c r="E30" s="46"/>
+      <x:c r="F30" s="69"/>
+      <x:c r="G30" s="46"/>
+      <x:c r="H30" s="46"/>
+      <x:c r="I30" s="46"/>
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
-      <x:c r="A31" s="60" t="str">
+      <x:c r="A31" s="67" t="str">
         <x:f>IF(C31="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B31" s="57"/>
-      <x:c r="C31" s="57"/>
-      <x:c r="D31" s="57"/>
-      <x:c r="E31" s="57"/>
-      <x:c r="F31" s="62"/>
-      <x:c r="G31" s="57"/>
-      <x:c r="H31" s="57"/>
-      <x:c r="I31" s="57"/>
+      <x:c r="B31" s="46"/>
+      <x:c r="C31" s="46"/>
+      <x:c r="D31" s="46"/>
+      <x:c r="E31" s="46"/>
+      <x:c r="F31" s="69"/>
+      <x:c r="G31" s="46"/>
+      <x:c r="H31" s="46"/>
+      <x:c r="I31" s="46"/>
     </x:row>
     <x:row r="32" ht="30" customHeight="1">
-      <x:c r="A32" s="60" t="str">
+      <x:c r="A32" s="67" t="str">
         <x:f>IF(C32="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B32" s="57"/>
-      <x:c r="C32" s="57"/>
-      <x:c r="D32" s="57"/>
-      <x:c r="E32" s="57"/>
-      <x:c r="F32" s="62"/>
-      <x:c r="G32" s="57"/>
-      <x:c r="H32" s="57"/>
-      <x:c r="I32" s="57"/>
+      <x:c r="B32" s="46"/>
+      <x:c r="C32" s="46"/>
+      <x:c r="D32" s="46"/>
+      <x:c r="E32" s="46"/>
+      <x:c r="F32" s="69"/>
+      <x:c r="G32" s="46"/>
+      <x:c r="H32" s="46"/>
+      <x:c r="I32" s="46"/>
     </x:row>
     <x:row r="33" ht="30" customHeight="1">
-      <x:c r="A33" s="60" t="str">
+      <x:c r="A33" s="67" t="str">
         <x:f>IF(C33="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B33" s="57"/>
-      <x:c r="C33" s="57"/>
-      <x:c r="D33" s="57"/>
-      <x:c r="E33" s="57"/>
-      <x:c r="F33" s="62"/>
-      <x:c r="G33" s="57"/>
-      <x:c r="H33" s="57"/>
-      <x:c r="I33" s="57"/>
+      <x:c r="B33" s="46"/>
+      <x:c r="C33" s="46"/>
+      <x:c r="D33" s="46"/>
+      <x:c r="E33" s="46"/>
+      <x:c r="F33" s="69"/>
+      <x:c r="G33" s="46"/>
+      <x:c r="H33" s="46"/>
+      <x:c r="I33" s="46"/>
     </x:row>
     <x:row r="34" ht="30" customHeight="1">
-      <x:c r="A34" s="60" t="str">
+      <x:c r="A34" s="67" t="str">
         <x:f>IF(C34="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B34" s="57"/>
-      <x:c r="C34" s="57"/>
-      <x:c r="D34" s="57"/>
-      <x:c r="E34" s="57"/>
-      <x:c r="F34" s="62"/>
-      <x:c r="G34" s="57"/>
-      <x:c r="H34" s="57"/>
-      <x:c r="I34" s="57"/>
+      <x:c r="B34" s="46"/>
+      <x:c r="C34" s="46"/>
+      <x:c r="D34" s="46"/>
+      <x:c r="E34" s="46"/>
+      <x:c r="F34" s="69"/>
+      <x:c r="G34" s="46"/>
+      <x:c r="H34" s="46"/>
+      <x:c r="I34" s="46"/>
     </x:row>
     <x:row r="35" ht="30" customHeight="1">
-      <x:c r="A35" s="60" t="str">
+      <x:c r="A35" s="67" t="str">
         <x:f>IF(C35="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B35" s="57"/>
-      <x:c r="C35" s="57"/>
-      <x:c r="D35" s="57"/>
-      <x:c r="E35" s="57"/>
-      <x:c r="F35" s="62"/>
-      <x:c r="G35" s="57"/>
-      <x:c r="H35" s="57"/>
-      <x:c r="I35" s="57"/>
+      <x:c r="B35" s="46"/>
+      <x:c r="C35" s="46"/>
+      <x:c r="D35" s="46"/>
+      <x:c r="E35" s="46"/>
+      <x:c r="F35" s="69"/>
+      <x:c r="G35" s="46"/>
+      <x:c r="H35" s="46"/>
+      <x:c r="I35" s="46"/>
     </x:row>
     <x:row r="36" ht="30" customHeight="1">
-      <x:c r="A36" s="60" t="str">
+      <x:c r="A36" s="67" t="str">
         <x:f>IF(C36="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B36" s="57"/>
-      <x:c r="C36" s="57"/>
-      <x:c r="D36" s="57"/>
-      <x:c r="E36" s="57"/>
-      <x:c r="F36" s="62"/>
-      <x:c r="G36" s="57"/>
-      <x:c r="H36" s="57"/>
-      <x:c r="I36" s="57"/>
+      <x:c r="B36" s="46"/>
+      <x:c r="C36" s="46"/>
+      <x:c r="D36" s="46"/>
+      <x:c r="E36" s="46"/>
+      <x:c r="F36" s="69"/>
+      <x:c r="G36" s="46"/>
+      <x:c r="H36" s="46"/>
+      <x:c r="I36" s="46"/>
     </x:row>
     <x:row r="37" ht="30" customHeight="1">
-      <x:c r="A37" s="60" t="str">
+      <x:c r="A37" s="67" t="str">
         <x:f>IF(C37="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B37" s="57"/>
-      <x:c r="C37" s="57"/>
-      <x:c r="D37" s="57"/>
-      <x:c r="E37" s="57"/>
-      <x:c r="F37" s="62"/>
-      <x:c r="G37" s="57"/>
-      <x:c r="H37" s="57"/>
-      <x:c r="I37" s="57"/>
+      <x:c r="B37" s="46"/>
+      <x:c r="C37" s="46"/>
+      <x:c r="D37" s="46"/>
+      <x:c r="E37" s="46"/>
+      <x:c r="F37" s="69"/>
+      <x:c r="G37" s="46"/>
+      <x:c r="H37" s="46"/>
+      <x:c r="I37" s="46"/>
     </x:row>
     <x:row r="38" ht="30" customHeight="1">
-      <x:c r="A38" s="60" t="str">
+      <x:c r="A38" s="67" t="str">
         <x:f>IF(C38="","",ROW()-8)</x:f>
       </x:c>
-      <x:c r="B38" s="57"/>
-      <x:c r="C38" s="57"/>
-      <x:c r="D38" s="57"/>
-      <x:c r="E38" s="57"/>
-      <x:c r="F38" s="62"/>
-      <x:c r="G38" s="57"/>
-      <x:c r="H38" s="57"/>
-      <x:c r="I38" s="57"/>
+      <x:c r="B38" s="46"/>
+      <x:c r="C38" s="46"/>
+      <x:c r="D38" s="46"/>
+      <x:c r="E38" s="46"/>
+      <x:c r="F38" s="69"/>
+      <x:c r="G38" s="46"/>
+      <x:c r="H38" s="46"/>
+      <x:c r="I38" s="46"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1395,10 +1643,10 @@
     <x:mergeCell ref="H4:I4"/>
   </x:mergeCells>
   <x:conditionalFormatting sqref="I9:I38">
-    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="通过"/>
-    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="已"/>
-    <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="待"/>
-    <x:cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="不通过"/>
+    <x:cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="通过"/>
+    <x:cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="已"/>
+    <x:cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="待"/>
+    <x:cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="不通过"/>
   </x:conditionalFormatting>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="B9:B38">
@@ -1410,7 +1658,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c2fe0f30a5e455a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R675b93240f744b08"/>
   </x:tableParts>
 </x:worksheet>
 </file>